--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20241.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -687,16 +678,19 @@
         <v>39</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>39</v>
       </c>
-      <c r="E2">
-        <v>39</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -710,16 +704,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>91.18000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -733,16 +730,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -756,16 +756,19 @@
         <v>23</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>23</v>
       </c>
-      <c r="E5">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -779,16 +782,19 @@
         <v>19</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>19</v>
       </c>
-      <c r="E6">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -802,16 +808,19 @@
         <v>10</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>10</v>
       </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -867,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>89.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -893,13 +902,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H3">
         <v>7.7</v>
@@ -919,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>75.76000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -945,16 +954,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>69.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -971,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1006,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1016,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1046,29 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>24330051920279</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
